--- a/forms/trg/Formulir_TRG_fsarg.xlsx
+++ b/forms/trg/Formulir_TRG_fsarg.xlsx
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B24" s="7">
-        <f>COUNTA(Anggota!B5:B27)</f>
+        <f>COUNTA(Anggota!B5:B28)</f>
         <v/>
       </c>
     </row>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!F5:F27)</f>
+        <f>COUNTA(Anggota!F5:F28)</f>
         <v/>
       </c>
     </row>
@@ -808,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M27"/>
+  <dimension ref="A1:M28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -913,30 +913,34 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Rianda Ridho Hafizh Thaha</t>
+          <t>Prof. Dr. Cepi Pahlevi, SE., MSi., CWM</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
-        </is>
-      </c>
-      <c r="D5" s="11" t="inlineStr">
-        <is>
-          <t>Faculty of Economics and Business, Hasanuddin University</t>
-        </is>
-      </c>
+          <t>Leader</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="n"/>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>Marketing Management</t>
+          <t>Financial Management</t>
         </is>
       </c>
       <c r="F5" s="12" t="n"/>
       <c r="G5" s="12" t="n"/>
       <c r="H5" s="12" t="n"/>
       <c r="I5" s="12" t="n"/>
-      <c r="J5" s="12" t="n"/>
-      <c r="K5" s="12" t="n"/>
+      <c r="J5" s="11" t="inlineStr">
+        <is>
+          <t>0000-0001-9055-0214</t>
+        </is>
+      </c>
+      <c r="K5" s="11" t="inlineStr">
+        <is>
+          <t>6024879</t>
+        </is>
+      </c>
       <c r="L5" s="12" t="n"/>
       <c r="M5" s="11" t="inlineStr">
         <is>
@@ -950,12 +954,12 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. Idayanti, SE., MSi., CWM</t>
+          <t>Rianda Ridho Hafizh Thaha</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
@@ -965,7 +969,7 @@
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>Human Resource Management</t>
+          <t>Marketing Management</t>
         </is>
       </c>
       <c r="F6" s="12" t="n"/>
@@ -987,12 +991,12 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. Mahlia Muis, SE., MSi., CIPM., CWM</t>
+          <t>Prof. Dr. Idayanti, SE., MSi., CWM</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
@@ -1024,22 +1028,22 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Dr. Ekhlas Khalid Abu-Sharkh.</t>
+          <t>Prof. Dr. Mahlia Muis, SE., MSi., CIPM., CWM</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>IHI (Institute for Health care organization)</t>
+          <t>Faculty of Economics and Business, Hasanuddin University</t>
         </is>
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>Human Resource Management</t>
         </is>
       </c>
       <c r="F8" s="12" t="n"/>
@@ -1061,22 +1065,22 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Hani Amer Musa Alaboodi</t>
+          <t>Dr. Ekhlas Khalid Abu-Sharkh.</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>BlackRock and Lion Emirates Global, Auckland, New Zealand</t>
+          <t>IHI (Institute for Health care organization)</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>Strategic Management, Business Development Consultant</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="F9" s="12" t="n"/>
@@ -1098,22 +1102,22 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. Mahlia Muis, SE., MSi., CIPM., CWM</t>
+          <t>Hani Amer Musa Alaboodi</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>Faculty of Economics and Business, Hasanuddin University</t>
+          <t>BlackRock and Lion Emirates Global, Auckland, New Zealand</t>
         </is>
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>Human Resource Management</t>
+          <t>Strategic Management, Business Development Consultant</t>
         </is>
       </c>
       <c r="F10" s="12" t="n"/>
@@ -1135,12 +1139,12 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. Idayanti, SE., MSi., CWM</t>
+          <t>Prof. Dr. Mahlia Muis, SE., MSi., CIPM., CWM</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
@@ -1172,12 +1176,12 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Rianda Ridho Hafizh Thaha</t>
+          <t>Prof. Dr. Idayanti, SE., MSi., CWM</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
@@ -1187,7 +1191,7 @@
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>Marketing Management</t>
+          <t>Human Resource Management</t>
         </is>
       </c>
       <c r="F12" s="12" t="n"/>
@@ -1209,12 +1213,12 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Helen Dias Andhini</t>
+          <t>Rianda Ridho Hafizh Thaha</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
@@ -1224,7 +1228,7 @@
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>Human Resource Management</t>
+          <t>Marketing Management</t>
         </is>
       </c>
       <c r="F13" s="12" t="n"/>
@@ -1246,12 +1250,12 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>M. Iqbal</t>
+          <t>Helen Dias Andhini</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
@@ -1261,7 +1265,7 @@
       </c>
       <c r="E14" s="11" t="inlineStr">
         <is>
-          <t>Financial Management</t>
+          <t>Human Resource Management</t>
         </is>
       </c>
       <c r="F14" s="12" t="n"/>
@@ -1283,12 +1287,12 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>Powell Gian Hartono</t>
+          <t>M. Iqbal</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
@@ -1298,7 +1302,7 @@
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>Corporate Finance, Investment, Corporate Governance, Behavioral Finance, and Business Management</t>
+          <t>Financial Management</t>
         </is>
       </c>
       <c r="F15" s="12" t="n"/>
@@ -1318,10 +1322,26 @@
       <c r="A16" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="12" t="n"/>
-      <c r="C16" s="12" t="n"/>
-      <c r="D16" s="12" t="n"/>
-      <c r="E16" s="11" t="n"/>
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>Powell Gian Hartono</t>
+        </is>
+      </c>
+      <c r="C16" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="D16" s="11" t="inlineStr">
+        <is>
+          <t>Faculty of Economics and Business, Hasanuddin University</t>
+        </is>
+      </c>
+      <c r="E16" s="11" t="inlineStr">
+        <is>
+          <t>Corporate Finance, Investment, Corporate Governance, Behavioral Finance, and Business Management</t>
+        </is>
+      </c>
       <c r="F16" s="12" t="n"/>
       <c r="G16" s="12" t="n"/>
       <c r="H16" s="12" t="n"/>
@@ -1329,7 +1349,11 @@
       <c r="J16" s="12" t="n"/>
       <c r="K16" s="12" t="n"/>
       <c r="L16" s="12" t="n"/>
-      <c r="M16" s="12" t="n"/>
+      <c r="M16" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
@@ -1518,15 +1542,32 @@
       <c r="L27" s="12" t="n"/>
       <c r="M27" s="12" t="n"/>
     </row>
+    <row r="28">
+      <c r="A28" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="B28" s="12" t="n"/>
+      <c r="C28" s="12" t="n"/>
+      <c r="D28" s="12" t="n"/>
+      <c r="E28" s="11" t="n"/>
+      <c r="F28" s="12" t="n"/>
+      <c r="G28" s="12" t="n"/>
+      <c r="H28" s="12" t="n"/>
+      <c r="I28" s="12" t="n"/>
+      <c r="J28" s="12" t="n"/>
+      <c r="K28" s="12" t="n"/>
+      <c r="L28" s="12" t="n"/>
+      <c r="M28" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
